--- a/Data_clean/MCAS/Estados_US/Edos_USA_2024/SOUTH_DAKOTA_2024.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2024/SOUTH_DAKOTA_2024.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D269"/>
+  <dimension ref="A1:D263"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Calvillo</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -421,9 +431,14 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pabellón de Arteaga</t>
+          <t>Pabellón De Arteaga</t>
         </is>
       </c>
       <c r="C5">
@@ -434,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Total</t>
@@ -465,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -478,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Total</t>
@@ -509,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Candelaria</t>
@@ -522,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Carmen</t>
@@ -535,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Champotón</t>
@@ -548,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Total</t>
@@ -579,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Arriaga</t>
@@ -592,9 +647,14 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bejucal de Ocampo</t>
+          <t>Bejucal De Ocampo</t>
         </is>
       </c>
       <c r="C17">
@@ -605,9 +665,14 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Benemérito de las Américas</t>
+          <t>Benemérito De Las Américas</t>
         </is>
       </c>
       <c r="C18">
@@ -618,9 +683,14 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Comitán de Domínguez</t>
+          <t>Comitán De Domínguez</t>
         </is>
       </c>
       <c r="C19">
@@ -631,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Escuintla</t>
@@ -644,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Frontera Comalapa</t>
@@ -657,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Huehuetán</t>
@@ -670,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -683,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Mapastepec</t>
@@ -696,9 +791,14 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mazapa de Madero</t>
+          <t>Mazapa De Madero</t>
         </is>
       </c>
       <c r="C25">
@@ -709,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Mitontic</t>
@@ -722,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Ocosingo</t>
@@ -735,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Ocotepec</t>
@@ -748,9 +863,14 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ocozocoautla de Espinosa</t>
+          <t>Ocozocoautla De Espinosa</t>
         </is>
       </c>
       <c r="C29">
@@ -761,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Reforma</t>
@@ -774,9 +899,14 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Salto de Agua</t>
+          <t>Salto De Agua</t>
         </is>
       </c>
       <c r="C31">
@@ -787,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>San Andrés Duraznal</t>
@@ -800,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Simojovel</t>
@@ -813,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -826,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Tuxtla Chico</t>
@@ -839,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Unión Juárez</t>
@@ -852,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Total</t>
@@ -883,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Chihuahua</t>
@@ -896,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Chínipas</t>
@@ -909,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -922,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -935,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Madera</t>
@@ -948,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Nuevo Casas Grandes</t>
@@ -961,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Total</t>
@@ -976,7 +1171,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -992,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -1005,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1018,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -1031,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -1044,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -1057,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1072,7 +1297,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Coahuila de Zaragoza</t>
+          <t>Coahuila De Zaragoza</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1088,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Coahuila De Zaragoza</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Piedras Negras</t>
@@ -1101,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Coahuila De Zaragoza</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>San Pedro</t>
@@ -1114,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Coahuila De Zaragoza</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Torreón</t>
@@ -1127,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Coahuila De Zaragoza</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1147,7 +1392,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>San Juan del Río</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C58">
@@ -1158,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -1171,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1186,12 +1441,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Almoloya de Juárez</t>
+          <t>Almoloya De Juárez</t>
         </is>
       </c>
       <c r="C61">
@@ -1202,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Chalco</t>
@@ -1215,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Chimalhuacán</t>
@@ -1228,9 +1493,14 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C64">
@@ -1241,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -1254,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Tejupilco</t>
@@ -1267,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Temascalcingo</t>
@@ -1280,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Texcoco</t>
@@ -1293,9 +1583,14 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C69">
@@ -1306,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -1319,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Villa Guerrero</t>
@@ -1332,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Villa Victoria</t>
@@ -1345,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Zinacantepec</t>
@@ -1358,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Zumpango</t>
@@ -1371,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1402,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Guanajuato</t>
@@ -1415,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -1428,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>León</t>
@@ -1441,9 +1781,14 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Purísima del Rincón</t>
+          <t>Purísima Del Rincón</t>
         </is>
       </c>
       <c r="C80">
@@ -1454,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Salamanca</t>
@@ -1467,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Salvatierra</t>
@@ -1480,9 +1835,14 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>San Francisco del Rincón</t>
+          <t>San Francisco Del Rincón</t>
         </is>
       </c>
       <c r="C83">
@@ -1493,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>San José Iturbide</t>
@@ -1506,9 +1871,14 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Santa Cruz de Juventino Rosas</t>
+          <t>Santa Cruz De Juventino Rosas</t>
         </is>
       </c>
       <c r="C85">
@@ -1519,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Tarimoro</t>
@@ -1532,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Villagrán</t>
@@ -1545,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Yuriria</t>
@@ -1558,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1578,7 +1968,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C90">
@@ -1589,9 +1979,14 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ajuchitlán del Progreso</t>
+          <t>Ajuchitlán Del Progreso</t>
         </is>
       </c>
       <c r="C91">
@@ -1602,9 +1997,14 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Atoyac de Álvarez</t>
+          <t>Atoyac De Álvarez</t>
         </is>
       </c>
       <c r="C92">
@@ -1615,9 +2015,14 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ayutla de los Libres</t>
+          <t>Ayutla De Los Libres</t>
         </is>
       </c>
       <c r="C93">
@@ -1628,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Azoyú</t>
@@ -1641,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Copalillo</t>
@@ -1654,9 +2069,14 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Coyuca de Catalán</t>
+          <t>Coyuca De Catalán</t>
         </is>
       </c>
       <c r="C96">
@@ -1667,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Cuajinicuilapa</t>
@@ -1680,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Eduardo Neri</t>
@@ -1693,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Leonardo Bravo</t>
@@ -1706,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Malinaltepec</t>
@@ -1719,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Ometepec</t>
@@ -1732,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Petatlán</t>
@@ -1745,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>San Miguel Totolapan</t>
@@ -1758,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Tlapehuala</t>
@@ -1771,9 +2231,14 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Técpan de Galeana</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C105">
@@ -1784,9 +2249,14 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Zihuatanejo de Azueta</t>
+          <t>Zihuatanejo De Azueta</t>
         </is>
       </c>
       <c r="C106">
@@ -1797,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1828,9 +2303,14 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C109">
@@ -1841,9 +2321,14 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Tula de Allende</t>
+          <t>Tula De Allende</t>
         </is>
       </c>
       <c r="C110">
@@ -1854,9 +2339,14 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Tulancingo de Bravo</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C111">
@@ -1867,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1898,9 +2393,14 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Atotonilco el Alto</t>
+          <t>Atotonilco El Alto</t>
         </is>
       </c>
       <c r="C114">
@@ -1911,9 +2411,14 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Autlán de Navarro</t>
+          <t>Autlán De Navarro</t>
         </is>
       </c>
       <c r="C115">
@@ -1924,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Ayotlán</t>
@@ -1937,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Ayutla</t>
@@ -1950,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Degollado</t>
@@ -1963,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Guachinango</t>
@@ -1976,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -1989,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -2002,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>La Barca</t>
@@ -2015,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>Mascota</t>
@@ -2028,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Ocotlán</t>
@@ -2041,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Poncitlán</t>
@@ -2054,9 +2609,14 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>San Diego de Alejandría</t>
+          <t>San Diego De Alejandría</t>
         </is>
       </c>
       <c r="C126">
@@ -2067,9 +2627,14 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>San Juan de los Lagos</t>
+          <t>San Juan De Los Lagos</t>
         </is>
       </c>
       <c r="C127">
@@ -2080,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Tala</t>
@@ -2093,9 +2663,14 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Tamazula de Gordiano</t>
+          <t>Tamazula De Gordiano</t>
         </is>
       </c>
       <c r="C129">
@@ -2106,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Tecalitlán</t>
@@ -2119,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Tecolotlán</t>
@@ -2132,9 +2717,14 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Tepatitlán de Morelos</t>
+          <t>Tepatitlán De Morelos</t>
         </is>
       </c>
       <c r="C132">
@@ -2145,9 +2735,14 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Tlajomulco de Zúñiga</t>
+          <t>Tlajomulco De Zúñiga</t>
         </is>
       </c>
       <c r="C133">
@@ -2158,6 +2753,11 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -2171,9 +2771,14 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Unión de San Antonio</t>
+          <t>Unión De San Antonio</t>
         </is>
       </c>
       <c r="C135">
@@ -2184,9 +2789,14 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Zacoalco de Torres</t>
+          <t>Zacoalco De Torres</t>
         </is>
       </c>
       <c r="C136">
@@ -2197,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -2210,6 +2825,11 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Zapotlanejo</t>
@@ -2223,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2238,7 +2863,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Michoacán de Ocampo</t>
+          <t>Michoacán De Ocampo</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -2254,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Coeneo</t>
@@ -2267,6 +2897,11 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -2280,6 +2915,11 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>Jacona</t>
@@ -2293,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Jungapeo</t>
@@ -2306,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -2319,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas</t>
@@ -2332,6 +2987,11 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>Puruándiro</t>
@@ -2345,6 +3005,11 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>Purépero</t>
@@ -2358,6 +3023,11 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>Senguio</t>
@@ -2371,6 +3041,11 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>Tangamandapio</t>
@@ -2384,6 +3059,11 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -2397,6 +3077,11 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>Tuzantla</t>
@@ -2410,6 +3095,11 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -2423,6 +3113,11 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>Yurécuaro</t>
@@ -2436,6 +3131,11 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -2449,6 +3149,11 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>Zinapécuaro</t>
@@ -2462,6 +3167,11 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -2475,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2506,6 +3221,11 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>Cuautla</t>
@@ -2519,6 +3239,11 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>Cuernavaca</t>
@@ -2532,6 +3257,11 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>Yautepec</t>
@@ -2545,6 +3275,11 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2576,6 +3311,11 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>Compostela</t>
@@ -2589,6 +3329,11 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>Tecuala</t>
@@ -2602,6 +3347,11 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -2615,6 +3365,11 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2646,6 +3401,11 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
           <t>Monterrey</t>
@@ -2659,6 +3419,11 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2679,7 +3444,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Acatlán de Pérez Figueroa</t>
+          <t>Acatlán De Pérez Figueroa</t>
         </is>
       </c>
       <c r="C172">
@@ -2690,9 +3455,14 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Guevea de Humboldt</t>
+          <t>Guevea De Humboldt</t>
         </is>
       </c>
       <c r="C173">
@@ -2703,9 +3473,14 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Juchitán de Zaragoza</t>
+          <t>Heroica Ciudad De Juchitán De Zaragoza</t>
         </is>
       </c>
       <c r="C174">
@@ -2716,9 +3491,14 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Huajuapan de León</t>
+          <t>Huajuapan De León</t>
         </is>
       </c>
       <c r="C175">
@@ -2729,6 +3509,11 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>Magdalena Jaltepec</t>
@@ -2742,6 +3527,11 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>San Carlos Yautepec</t>
@@ -2755,6 +3545,11 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>San Juan Bautista Cuicatlán</t>
@@ -2768,6 +3563,11 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
           <t>San Lorenzo</t>
@@ -2781,6 +3581,11 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>San Lorenzo Texmelúcan</t>
@@ -2794,6 +3599,11 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
           <t>San Pedro Pochutla</t>
@@ -2807,6 +3617,11 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>Santa María Huatulco</t>
@@ -2820,6 +3635,11 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
           <t>Santa María Tonameca</t>
@@ -2833,6 +3653,11 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>Santiago Pinotepa Nacional</t>
@@ -2846,6 +3671,11 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>Santo Domingo Tonalá</t>
@@ -2859,6 +3689,11 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2890,6 +3725,11 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
           <t>Aquixtla</t>
@@ -2903,6 +3743,11 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
           <t>Chichiquila</t>
@@ -2916,6 +3761,11 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>Chignahuapan</t>
@@ -2929,6 +3779,11 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
           <t>Coatzingo</t>
@@ -2942,6 +3797,11 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
           <t>Nicolás Bravo</t>
@@ -2955,6 +3815,11 @@
       </c>
     </row>
     <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
           <t>Tenampulco</t>
@@ -2968,6 +3833,11 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>Tilapa</t>
@@ -2981,6 +3851,11 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>Tlapacoya</t>
@@ -2994,6 +3869,11 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -3007,6 +3887,11 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>Xicotepec</t>
@@ -3020,6 +3905,11 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>Zacapoaxtla</t>
@@ -3033,6 +3923,11 @@
       </c>
     </row>
     <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
           <t>Zacatlán</t>
@@ -3046,6 +3941,11 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
           <t>Zautla</t>
@@ -3059,6 +3959,11 @@
       </c>
     </row>
     <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B201" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3090,6 +3995,11 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -3103,6 +4013,11 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3134,6 +4049,11 @@
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -3147,9 +4067,14 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Santa María del Río</t>
+          <t>Santa María Del Río</t>
         </is>
       </c>
       <c r="C207">
@@ -3160,6 +4085,11 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>Villa Hidalgo</t>
@@ -3173,9 +4103,14 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Villa de Arista</t>
+          <t>Villa De Arista</t>
         </is>
       </c>
       <c r="C209">
@@ -3186,9 +4121,14 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Villa de Ramos</t>
+          <t>Villa De Ramos</t>
         </is>
       </c>
       <c r="C210">
@@ -3199,6 +4139,11 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3230,6 +4175,11 @@
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
           <t>Cosalá</t>
@@ -3243,6 +4193,11 @@
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
           <t>Elota</t>
@@ -3256,6 +4211,11 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3287,6 +4247,11 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
           <t>Cárdenas</t>
@@ -3300,6 +4265,11 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
           <t>Emiliano Zapata</t>
@@ -3313,6 +4283,11 @@
       </c>
     </row>
     <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3344,6 +4319,11 @@
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
           <t>Victoria</t>
@@ -3357,6 +4337,11 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3388,6 +4373,11 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
           <t>Hueyotlipan</t>
@@ -3401,6 +4391,11 @@
       </c>
     </row>
     <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
           <t>Tlaxcala</t>
@@ -3414,6 +4409,11 @@
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3429,7 +4429,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Veracruz de Ignacio de la Llave</t>
+          <t>Veracruz De Ignacio De La Llave</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -3445,6 +4445,11 @@
       </c>
     </row>
     <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
           <t>Altotonga</t>
@@ -3458,6 +4463,11 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
           <t>Atzalan</t>
@@ -3471,6 +4481,11 @@
       </c>
     </row>
     <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -3484,6 +4499,11 @@
       </c>
     </row>
     <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
           <t>Chocamán</t>
@@ -3497,6 +4517,11 @@
       </c>
     </row>
     <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
           <t>Coscomatepec</t>
@@ -3510,6 +4535,11 @@
       </c>
     </row>
     <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B233" t="inlineStr">
         <is>
           <t>Cosoleacaque</t>
@@ -3523,6 +4553,11 @@
       </c>
     </row>
     <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -3536,9 +4571,14 @@
       </c>
     </row>
     <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Ignacio de la Llave</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C235">
@@ -3549,6 +4589,11 @@
       </c>
     </row>
     <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
           <t>Las Choapas</t>
@@ -3562,6 +4607,11 @@
       </c>
     </row>
     <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
           <t>Manlio Fabio Altamirano</t>
@@ -3575,9 +4625,14 @@
       </c>
     </row>
     <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C238">
@@ -3588,6 +4643,11 @@
       </c>
     </row>
     <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
           <t>Misantla</t>
@@ -3601,9 +4661,14 @@
       </c>
     </row>
     <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Mixtla de Altamirano</t>
+          <t>Mixtla De Altamirano</t>
         </is>
       </c>
       <c r="C240">
@@ -3614,6 +4679,11 @@
       </c>
     </row>
     <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
           <t>Naolinco</t>
@@ -3627,6 +4697,11 @@
       </c>
     </row>
     <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
           <t>Nautla</t>
@@ -3640,9 +4715,14 @@
       </c>
     </row>
     <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Paso de Ovejas</t>
+          <t>Paso De Ovejas</t>
         </is>
       </c>
       <c r="C243">
@@ -3653,6 +4733,11 @@
       </c>
     </row>
     <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
           <t>San Juan Evangelista</t>
@@ -3666,9 +4751,14 @@
       </c>
     </row>
     <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Sayula de Alemán</t>
+          <t>Sayula De Alemán</t>
         </is>
       </c>
       <c r="C245">
@@ -3679,6 +4769,11 @@
       </c>
     </row>
     <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
           <t>Soledad Atzompa</t>
@@ -3692,9 +4787,14 @@
       </c>
     </row>
     <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Soledad de Doblado</t>
+          <t>Soledad De Doblado</t>
         </is>
       </c>
       <c r="C247">
@@ -3705,6 +4805,11 @@
       </c>
     </row>
     <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B248" t="inlineStr">
         <is>
           <t>Tezonapa</t>
@@ -3718,6 +4823,11 @@
       </c>
     </row>
     <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B249" t="inlineStr">
         <is>
           <t>Tlapacoyan</t>
@@ -3731,6 +4841,11 @@
       </c>
     </row>
     <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -3744,6 +4859,11 @@
       </c>
     </row>
     <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr">
         <is>
           <t>Zongolica</t>
@@ -3757,6 +4877,11 @@
       </c>
     </row>
     <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B252" t="inlineStr">
         <is>
           <t>Álamo Temapache</t>
@@ -3770,6 +4895,11 @@
       </c>
     </row>
     <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3801,6 +4931,11 @@
       </c>
     </row>
     <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr">
         <is>
           <t>Fresnillo</t>
@@ -3814,6 +4949,11 @@
       </c>
     </row>
     <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
           <t>Pinos</t>
@@ -3827,6 +4967,11 @@
       </c>
     </row>
     <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B257" t="inlineStr">
         <is>
           <t>Sombrerete</t>
@@ -3840,9 +4985,14 @@
       </c>
     </row>
     <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Trinidad García de la Cadena</t>
+          <t>Trinidad García De La Cadena</t>
         </is>
       </c>
       <c r="C258">
@@ -3853,6 +5003,11 @@
       </c>
     </row>
     <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B259" t="inlineStr">
         <is>
           <t>Valparaíso</t>
@@ -3866,9 +5021,14 @@
       </c>
     </row>
     <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Villa de Cos</t>
+          <t>Villa De Cos</t>
         </is>
       </c>
       <c r="C260">
@@ -3879,6 +5039,11 @@
       </c>
     </row>
     <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B261" t="inlineStr">
         <is>
           <t>Zacatecas</t>
@@ -3892,6 +5057,11 @@
       </c>
     </row>
     <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3907,7 +5077,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C263">
@@ -3915,41 +5085,6 @@
       </c>
       <c r="D263">
         <v>1</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 808,027</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de Mexicanas y Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>Junio de 2025</t>
-        </is>
       </c>
     </row>
   </sheetData>
